--- a/am-hub-final/static/diginetica-api-keys-template.xlsx
+++ b/am-hub-final/static/diginetica-api-keys-template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,13 +30,31 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="006474FF"/>
-      <sz val="10"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0023D18B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00F5A623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B36BFF"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
       <i val="1"/>
-      <color rgb="007D8AAA"/>
-      <sz val="9"/>
+      <color rgb="004C567A"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -46,6 +64,16 @@
     <font>
       <name val="Courier New"/>
       <color rgb="0023D18B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="00F5A623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Courier New"/>
+      <color rgb="004CA5FF"/>
       <sz val="9"/>
     </font>
     <font>
@@ -57,7 +85,7 @@
     <font>
       <name val="Arial"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -68,15 +96,45 @@
     <font>
       <name val="Arial"/>
       <color rgb="007D8AAA"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0023D18B"/>
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000A2318"/>
+        <bgColor rgb="000A2318"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A1E08"/>
+        <bgColor rgb="002A1E08"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A0F2A"/>
+        <bgColor rgb="001A0F2A"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -97,7 +155,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -105,42 +163,63 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <right style="thin">
-        <color rgb="001E2840"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="006474FF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -506,143 +585,262 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" ht="36" customHeight="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Sort (поиск)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Autocomplete</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Recommendations</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Дополнительно</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
           <t>client_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>client_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>diginetica_api_key</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>sort_api_key</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>sort_url</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>auto_api_key</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>auto_url</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>rec_api_key</t>
+        </is>
+      </c>
+      <c r="H2" s="8" t="inlineStr">
+        <is>
+          <t>rec_url</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>site_url</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>checkup_queries_top</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>ID клиента в AM Hub
-(число из URL /client/ID)</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Название клиента
-(для сверки)</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Diginetica API Key
-(apiKey для поиска)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>URL сайта клиента
-(необязательно)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Запросы TOP
-(через запятую, необязательно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="3" t="n">
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Число из URL /client/42</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Только для проверки</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Ключ Diginetica Sort Search</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>https://sort.diginetica.net/search</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>Ключ Diginetica Autocomplete</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>https://...diginetica.net/...</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Ключ Diginetica Rec</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
+        <is>
+          <t>https://...diginetica.net/...</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>https://client.ru</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>пуховик, куртка, джинсы</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>ООО Ромашка</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>a1b2c3d4e5f6a1b2c3d4e5f6a1b2c3d4</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>a1b2c3d4e5f6a1b2c3d4e5f6</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>https://sort.diginetica.net/search</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>a1b2c3d4e5f6a1b2auto0000</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="10" t="inlineStr"/>
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>https://romashka.ru</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>пуховик,куртка,джинсы,кроссовки</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="5" t="n">
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>пуховик,куртка,джинсы</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="13" t="n">
         <v>117</v>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Магазин Техника</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>x9y8z7w6v5u4x9y8z7w6v5u4x9y8z7w6</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Техника Плюс</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>x9y8z7w6v5u4x9y8z7w6v5u4</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr"/>
+      <c r="E5" s="13" t="inlineStr"/>
+      <c r="F5" s="13" t="inlineStr"/>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>x9y8z7w6v5u4recrpqqq0000</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>https://recs.diginetica.net/recommend</t>
+        </is>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>https://technika.ru</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>смартфон,ноутбук,наушники</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="n">
+      <c r="J5" s="13" t="inlineStr">
+        <is>
+          <t>смартфон,ноутбук</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Детский мир Плюс</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>q1w2e3r4t5y6q1w2e3r4t5y6q1w2e3r4</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Детский мир</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>q1w2e3r4t5y6q1w2e3r4t5y6</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr"/>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>q1w2e3r4t5y6auto0000aaaa</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="I1:J1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -653,116 +851,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>AM Hub — Импорт Diginetica API Keys</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="8" t="inlineStr"/>
-    </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Как заполнить файл:</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>1. client_id — число из URL страницы клиента: /client/42 → 42</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
-        <is>
-          <t>2. client_name — название для вашей сверки, AM Hub использует только client_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>3. diginetica_api_key — ключ из личного кабинета Diginetica клиента</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>4. site_url — URL сайта клиента (необязательно, для расширения)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>5. checkup_queries_top — запросы через запятую для чекапа (необязательно)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Как загрузить:</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>AM Hub → Настройки → Администратор → Импорт API Keys → загрузить этот файл</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="8" t="inlineStr"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Примечания:</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>• Строки без client_id будут пропущены</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t>• Если клиент не найден по ID — будет указано в отчёте</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>• Поле доступно только администраторам (менеджеры могут только копировать)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>• После загрузки данные сразу доступны в расширении Search Quality Checkup</t>
+    <row r="1" ht="17" customHeight="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>AM Hub — Импорт Diginetica API Keys v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="17" customHeight="1">
+      <c r="A2" s="17" t="inlineStr"/>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>КОЛОНКИ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>client_id — число из URL клиента: /client/42 → 42. Обязательное поле.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>client_name — только для вашей сверки, AM Hub использует только ID.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="17" t="inlineStr"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>ПРОДУКТЫ DIGINETICA:</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>sort_api_key / sort_url — ключ и URL для Sort Search (основной поиск)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>auto_api_key / auto_url — ключ и URL для Autocomplete (автодополнение)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>rec_api_key / rec_url — ключ и URL для Recommendations (рекомендации)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Заполняйте только те продукты, которые подключены у клиента.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="17" t="inlineStr"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>ДОПОЛНИТЕЛЬНО:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>site_url — URL сайта клиента (для расширения, необязательно)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>checkup_queries_top — запросы через запятую для чекапа поиска</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="17" t="inlineStr"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>КАК ЗАГРУЗИТЬ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>AM Hub → Администратор → Импорт API Keys → загрузить этот файл</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="17" t="inlineStr"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>ПРИМЕЧАНИЯ:</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>• Строки без client_id пропускаются</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>• URL-поля необязательны — если пусто, используется дефолтный URL Diginetica</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>• После загрузки ключи доступны в расширении Search Quality Checkup</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>• Менеджеры видят только маску ключа, редактируют только администраторы</t>
         </is>
       </c>
     </row>
